--- a/data/sku_mapping.xlsx
+++ b/data/sku_mapping.xlsx
@@ -2976,74 +2976,38 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
-        <x:v>TSHWE230-12K-32-I</x:v>
+        <x:v>TSHWE230-12K-32-I/O</x:v>
       </x:c>
       <x:c r="B2" t="str"/>
       <x:c r="C2" t="str">
         <x:v>TSHWE230-12K-32-I</x:v>
       </x:c>
       <x:c r="D2" t="str">
-        <x:v>分体空调室内机/主SKU，I/O两箱归并</x:v>
+        <x:v>RTV整机产品SKU；实际发货分为-I和-O两个箱子</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
-        <x:v>TSHWE230-12K-32-O</x:v>
+        <x:v>ASHWM115-12K-I/O</x:v>
       </x:c>
       <x:c r="B3" t="str"/>
       <x:c r="C3" t="str">
-        <x:v>TSHWE230-12K-32-I</x:v>
+        <x:v>ASHWM115-12K-I</x:v>
       </x:c>
       <x:c r="D3" t="str">
-        <x:v>分体空调另一箱，与-I归并</x:v>
+        <x:v>RTV整机产品SKU；实际发货分为-I和-O两个箱子</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
-        <x:v>ASHWM115-12K-I</x:v>
+        <x:v>ASHWM230-18K-I/O</x:v>
       </x:c>
       <x:c r="B4" t="str"/>
       <x:c r="C4" t="str">
-        <x:v>ASHWM115-12K-I</x:v>
+        <x:v>ASHWM230-18K-I</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>分体空调室内机/主SKU，I/O两箱归并</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="str">
-        <x:v>ASHWM115-12K-O</x:v>
-      </x:c>
-      <x:c r="B5" t="str"/>
-      <x:c r="C5" t="str">
-        <x:v>ASHWM115-12K-I</x:v>
-      </x:c>
-      <x:c r="D5" t="str">
-        <x:v>分体空调另一箱，与-I归并</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="str">
-        <x:v>ASHWM230-18K-I</x:v>
-      </x:c>
-      <x:c r="B6" t="str"/>
-      <x:c r="C6" t="str">
-        <x:v>ASHWM230-18K-I</x:v>
-      </x:c>
-      <x:c r="D6" t="str">
-        <x:v>分体空调室内机/主SKU，I/O两箱归并</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str">
-        <x:v>ASHWM230-18K-O</x:v>
-      </x:c>
-      <x:c r="B7" t="str"/>
-      <x:c r="C7" t="str">
-        <x:v>ASHWM230-18K-I</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>分体空调另一箱，与-I归并</x:v>
+        <x:v>RTV整机产品SKU；实际发货分为-I和-O两个箱子</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
